--- a/docs/01_新闻类型分类评判表.xlsx
+++ b/docs/01_新闻类型分类评判表.xlsx
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.02复核修订" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.03复核修订" sheetId="40" state="visible" r:id="rId40"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.04复核修订" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1.10载体前提" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -13823,7 +13824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14624,6 +14625,33 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>『极电光能确认演讲』→ T24；『氢用压力管道规范』→ T20；『首钢朗泽商业化运营』→ T08；『塑料热解工厂关闭』不再误 T13；『品牌矩阵』不再误 T01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C-T16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>载体前提（2026-09-24 用户口径）</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DOI×语义共决：literature 一律文献；非文献源有 DOI ≠ 论文</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>前提① literature 库一律 T01（文献 RSS 载体身份优先）；前提② wechat/news-spider 的 DOI（字段/链接/正文）只是引用线索，不构成文献载体：论文本体载体（《刊名》文章/全文转载/学术速递/网络首发/引用本文）或题名期刊锚定＋学术命题 → 可 T01；DOI 迹象×题名媒体分析/报道框架（解读/评述/盘点/梳理/综述：/科普/评论/观点/Top N/据报道/科学家发现/Scientists discover/study shows 等）→ 非文献，改判 T23 深度分析（题名锚定，与 M1 同口径），DOI 记入证据链</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>『Scientists Discover …（正文附 doi.org 链接）』→ T23；『深度解读：××机理（正文 DOI）』→ T23；『一周顶刊盘点 Top10』→ T23；『《储能科学与技术》文章｜××（全文转载）』→ T01；『学术速递｜××』→ T01</t>
         </is>
       </c>
     </row>
@@ -17479,6 +17507,151 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="150" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>v1.10 载体前提（2026-09-24，用户口径：有 DOI 不一定是文献，可能是分析——DOI×语义共决）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C-T16 载体前提（build_strict_semantic_triage.classify_type_semantic，位于 T24/T21-期刊指标/T21-招聘 早退之后、T01 add 之前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>前提① literature 一律文献</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>src=literature → T01（函数入口既有早退，v1.10 升格为前提规则显式化；LLM 约束 3 同口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>前提② DOI 只是引用线索</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>doi_signal = doi 字段 ∨ 题名/正文/url 命中 10.xxxx/arXiv/DOI/doi.org——只作共决线索，不再单独构成论文载体（原 paper_carrier 的正文级 DOI 正则已移除；T01 门改为 paper_body_carrier〔本体载体〕∨ paper_structure〔题名/导语结构锚定〕＋学术命题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>本体载体（可 T01）</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>《刊名》文章/全文转载/学术速递/论文速递/研究进展速递/文献速递/网络首发/引用本文（题名+导语级）；或题名期刊锚定（JACS/Nature/Angew/EES 等）＋学术命题且无转述框架（v1.06 口径不变）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C-T16 改判（→T23）</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>doi_signal ∧ 题名媒体分析/报道框架 ∧ 学术命题 ∧ 非本体载体 → T23 深度分析，审计留痕『C-G05/C-T16-DOI载体前提』，DOI 记入证据链。框架词：解读|评述|评析|剖析|深度分析|盘点|梳理|知识分享|一文读懂|科普|评论|观点|详解|拆解|综述[：:｜]|Top N|周榜|月榜|据报道/据了解|科学家发现/揭示|Scientists discover/find/reveal/turn|study shows/finds/reveals/suggests</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>证据级收窄</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>_evidence_level：E1『论文/DOI 原始载体』仅 literature 源；wechat/news 带 DOI 字段 → E2『报道引用论文 DOI（二手可溯源）』（v1.10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LLM 契约 v3.1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run_llm SYSTEM_PROMPT 约束 3 增补【v3.1 载体前提】：src=literature 一律 T01；wechat/news 的 DOI 只是引用线索——仅论文本体（全文转载/速递/题名即论文/正文即摘要）才 T01；报道/解读/分析附 DOI 按主事件分型（多为 T23）。decisions 版本串 2026-09-24-v3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>已知边界</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>①框架词以题名为准（与 M1 题名锚定同口径），导语级框架不触发改判；②DOI 无任何框架词且题名/导语有期刊锚定 → 仍可 T01（期刊锚定题名＝论文式题名）；③事件级去重 C-R01 跨源 DOI 合并不变（同 DOI=同论文事件，主记录择优）；④四批数据（06-24~27）wechat/news DOI 痕迹为 0，本规则为前瞻防线，效果将由后续批次回测</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>验证（2026-09-24）</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>verify_v110_doi_carrier：9/9 合成案例＋3 项契约全过；三测试批重建——06-26 零漂移；06-25《储能科学与技术》文章（全文转载）T25→T01·中·P0（本体载体 rescue，符合意图）；06-27『本周学术文章Top10』T01·中→T23·参考（C-T16 首个实战命中，盘点合辑退出论文档）；其余 11 套回归全绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>常数状态</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>框架词表/本体载体词表为草案（v1.10 用户口径直译），单源在 build_strict_semantic_triage.py（media_analysis_frame / paper_body_carrier / doi_signal）；待后续批次回测校准</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
